--- a/data/raw/campaigns.xlsx
+++ b/data/raw/campaigns.xlsx
@@ -575,7 +575,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
